--- a/PerformanceReports/SET_PERFORMANCE_API_REPORT.xlsx
+++ b/PerformanceReports/SET_PERFORMANCE_API_REPORT.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="66">
   <si>
     <t xml:space="preserve">Run Number</t>
   </si>
@@ -177,6 +177,15 @@
     <t xml:space="preserve">10:46:25</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprint_217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:43:53</t>
+  </si>
+  <si>
     <t xml:space="preserve">11:22:51</t>
   </si>
   <si>
@@ -192,6 +201,9 @@
     <t xml:space="preserve">15:05:38</t>
   </si>
   <si>
+    <t xml:space="preserve">16:20:40</t>
+  </si>
+  <si>
     <t xml:space="preserve">21:17:41</t>
   </si>
   <si>
@@ -208,6 +220,9 @@
   </si>
   <si>
     <t xml:space="preserve">11:37:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:50:56</t>
   </si>
 </sst>
 </file>
@@ -598,7 +613,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="35.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.57"/>
@@ -1141,6 +1156,62 @@
         <v>1</v>
       </c>
       <c r="S11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>-13.04</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1175,10 +1246,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.71"/>
@@ -1293,11 +1364,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.71"/>
@@ -1423,7 +1494,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>5</v>
@@ -1467,7 +1538,7 @@
         <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>100</v>
@@ -1511,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>100</v>
@@ -1567,7 +1638,7 @@
         <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>100</v>
@@ -1623,7 +1694,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>100</v>
@@ -1665,6 +1736,62 @@
         <v>1</v>
       </c>
       <c r="S7" s="1" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -1685,10 +1812,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.71"/>
@@ -1804,10 +1931,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.71"/>
@@ -1932,7 +2059,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>100</v>
@@ -1976,7 +2103,7 @@
         <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>100</v>
@@ -2020,7 +2147,7 @@
         <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>100</v>
@@ -2076,7 +2203,7 @@
         <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>100</v>
@@ -2121,7 +2248,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -2129,10 +2256,10 @@
         <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>100</v>
@@ -2175,6 +2302,62 @@
       </c>
       <c r="S7" s="1" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2204,10 +2387,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.71"/>

--- a/PerformanceReports/SET_PERFORMANCE_API_REPORT.xlsx
+++ b/PerformanceReports/SET_PERFORMANCE_API_REPORT.xlsx
@@ -118,7 +118,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -156,6 +156,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,7 +410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.68" customWidth="1" style="5" min="1" max="1"/>
@@ -565,27 +566,27 @@
       <c r="G2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="5" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="6">
       <c r="A3" s="5" t="n">
@@ -636,12 +637,12 @@
       <c r="N3" s="5" t="n">
         <v>-52</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="6">
       <c r="A4" s="5" t="n">
@@ -692,12 +693,12 @@
       <c r="N4" s="5" t="n">
         <v>-8.33</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="6">
       <c r="A5" s="5" t="n">
@@ -748,12 +749,12 @@
       <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="6">
       <c r="A6" s="5" t="n">
@@ -804,12 +805,12 @@
       <c r="N6" s="5" t="n">
         <v>4.55</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="6">
       <c r="A7" s="5" t="n">
@@ -860,12 +861,12 @@
       <c r="N7" s="5" t="n">
         <v>4.35</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="6">
       <c r="A8" s="5" t="n">
@@ -916,12 +917,12 @@
       <c r="N8" s="5" t="n">
         <v>-8.33</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="6">
       <c r="A9" s="5" t="n">
@@ -978,14 +979,14 @@
       <c r="P9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="S9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="6">
       <c r="A10" s="5" t="n">
@@ -1042,14 +1043,14 @@
       <c r="P10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="S10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="6">
       <c r="A11" s="5" t="n">
@@ -1106,14 +1107,14 @@
       <c r="P11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="6">
       <c r="A12" s="5" t="n">
@@ -1170,78 +1171,142 @@
       <c r="P12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="S12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Sprint_rn_1600</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>19:23:28</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.34</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="5" t="n">
         <v>-30.61</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="5" t="n">
         <v>-17.5</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="L13" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="5" t="n">
         <v>0.23</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="O13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sprint_rn_9129</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>18:47:37</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="1048563" ht="12.75" customHeight="1" s="6"/>
     <row r="1048564" ht="12.75" customHeight="1" s="6"/>
